--- a/output/pdf_financials_xlsx/BEK.B.xlsx
+++ b/output/pdf_financials_xlsx/BEK.B.xlsx
@@ -24369,7 +24369,7 @@
         <v>-0.778354</v>
       </c>
       <c r="T152" s="5" t="n">
-        <v>0.124478</v>
+        <v>-0.124478</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BEK.B.xlsx
+++ b/output/pdf_financials_xlsx/BEK.B.xlsx
@@ -971,52 +971,52 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.606301</v>
+        <v>1.862403</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.560261</v>
+        <v>1.739492</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.529822</v>
+        <v>1.627181</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.519826</v>
+        <v>2.211154</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.476715</v>
+        <v>1.806311</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.513103</v>
+        <v>1.805066</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.540637</v>
+        <v>1.856657</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.552079</v>
+        <v>1.745822</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.548477</v>
+        <v>1.771302</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.467751</v>
+        <v>1.688764</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.657134</v>
+        <v>2.077254</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.508281</v>
+        <v>1.983663</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.418065</v>
+        <v>1.756874</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.417676</v>
+        <v>1.715359</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.447559</v>
+        <v>1.755252</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.501429</v>
+        <v>1.874706</v>
       </c>
     </row>
     <row r="11">
@@ -1036,52 +1036,52 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.433959</v>
+        <v>2.177857</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.553636</v>
+        <v>2.374405</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.559213</v>
+        <v>2.461854</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3.428983</v>
+        <v>1.737655</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.492181</v>
+        <v>2.162585</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>3.273154</v>
+        <v>1.981191</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.138629</v>
+        <v>1.822609</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>2.741118</v>
+        <v>1.547375</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2.595163</v>
+        <v>1.372338</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2.706413</v>
+        <v>1.4854</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.440021</v>
+        <v>1.019901</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.161761</v>
+        <v>0.686379</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.44237</v>
+        <v>1.103561</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>2.627972</v>
+        <v>1.330289</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>2.544523</v>
+        <v>1.23683</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>2.52327</v>
+        <v>1.149993</v>
       </c>
     </row>
     <row r="12">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
